--- a/data/trans_orig/P57B6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023</t>
+          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211377</t>
+          <t>215333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282394</t>
+          <t>282701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145996</t>
+          <t>145477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194623</t>
+          <t>191331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>376239</t>
+          <t>377213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>456874</t>
+          <t>462733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88202</t>
+          <t>87984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155075</t>
+          <t>154611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79424</t>
+          <t>82861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>127154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185803</t>
+          <t>181321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265997</t>
+          <t>260239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44529</t>
+          <t>47475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44307</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89594</t>
+          <t>89477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>158102</t>
+          <t>158647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110370</t>
+          <t>100693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215231</t>
+          <t>214697</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>280130</t>
+          <t>273884</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405428</t>
+          <t>408587</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158454</t>
+          <t>159944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212476</t>
+          <t>212986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193871</t>
+          <t>191893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>357810</t>
+          <t>354935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377278</t>
+          <t>376846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>545108</t>
+          <t>541322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56058</t>
+          <t>53216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49445</t>
+          <t>49338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85833</t>
+          <t>87406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>143423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43519</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226182</t>
+          <t>227677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276578</t>
+          <t>276280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177748</t>
+          <t>174644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>213336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412481</t>
+          <t>412782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>476718</t>
+          <t>475573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173773</t>
+          <t>177194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221752</t>
+          <t>222156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>206630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>243473</t>
+          <t>247121</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>392012</t>
+          <t>394938</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>455157</t>
+          <t>454661</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55645</t>
+          <t>54987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87358</t>
+          <t>86552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>110960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145590</t>
+          <t>145559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>190865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>328918</t>
+          <t>334370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>715589</t>
+          <t>714982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>164734</t>
+          <t>162566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>216720</t>
+          <t>214288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>509252</t>
+          <t>509211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1067932</t>
+          <t>1055683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123098</t>
+          <t>126626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>404744</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315186</t>
+          <t>316919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>402814</t>
+          <t>400010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376018</t>
+          <t>377167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>760201</t>
+          <t>760832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>40449</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142545</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>125221</t>
+          <t>124900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>172722</t>
+          <t>171472</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141056</t>
+          <t>150506</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296940</t>
+          <t>304296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22605</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176619</t>
+          <t>178164</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>219861</t>
+          <t>221171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>132647</t>
+          <t>130276</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163608</t>
+          <t>161949</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>320706</t>
+          <t>320498</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>372747</t>
+          <t>373304</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>234651</t>
+          <t>232938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>277588</t>
+          <t>276274</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224447</t>
+          <t>224106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258347</t>
+          <t>258405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>470072</t>
+          <t>471109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>525966</t>
+          <t>527450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107923</t>
+          <t>107325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116928</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148186</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>202674</t>
+          <t>199783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>245759</t>
+          <t>243178</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53299</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118723</t>
+          <t>117976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>148795</t>
+          <t>149332</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>180562</t>
+          <t>181836</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122446</t>
+          <t>128240</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>323252</t>
+          <t>324476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>156657</t>
+          <t>156196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>187180</t>
+          <t>186424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>276841</t>
+          <t>275508</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>516185</t>
+          <t>511952</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>446783</t>
+          <t>445288</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>780488</t>
+          <t>757698</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46570</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>137499</t>
+          <t>137909</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71660</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>188807</t>
+          <t>188239</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>75812</t>
+          <t>76622</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>101657</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>68209</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>89495</t>
+          <t>91450</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>151000</t>
+          <t>150788</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>185035</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>118994</t>
+          <t>117156</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>145157</t>
+          <t>144031</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>188131</t>
+          <t>188119</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>216565</t>
+          <t>217265</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>315820</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>355043</t>
+          <t>353855</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64847</t>
+          <t>66372</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>112904</t>
+          <t>113492</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139782</t>
+          <t>139662</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>162397</t>
+          <t>163182</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>195843</t>
+          <t>196199</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1441229</t>
+          <t>1438132</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2037692</t>
+          <t>2033608</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>863945</t>
+          <t>870466</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1166183</t>
+          <t>1178093</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2437103</t>
+          <t>2426709</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3169589</t>
+          <t>3146648</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1015563</t>
+          <t>1025184</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1465567</t>
+          <t>1466512</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1611689</t>
+          <t>1598905</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2115945</t>
+          <t>2131137</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>3099078</t>
+          <t>3099079</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2798712</t>
+          <t>2799199</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3414110</t>
+          <t>3491270</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>335889</t>
+          <t>330959</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>484064</t>
+          <t>488097</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>574740</t>
+          <t>569020</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>766299</t>
+          <t>770538</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>998685</t>
+          <t>984445</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1232608</t>
+          <t>1235354</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>52758</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>93915</t>
+          <t>92291</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133728</t>
+          <t>133989</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>157139</t>
+          <t>153923</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>216010</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">

--- a/data/trans_orig/P57B6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>251007</t>
+          <t>256144</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215333</t>
+          <t>223361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282701</t>
+          <t>286571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>169652</t>
+          <t>192939</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>166194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191331</t>
+          <t>219567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>420659</t>
+          <t>449082</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>404217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462733</t>
+          <t>488112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>117478</t>
+          <t>120256</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87984</t>
+          <t>92512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154611</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>103060</t>
+          <t>123110</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82861</t>
+          <t>98117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127154</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>220539</t>
+          <t>243366</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181321</t>
+          <t>208321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260239</t>
+          <t>285098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47475</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53198</t>
+          <t>61133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63270</t>
+          <t>69781</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395777</t>
+          <t>404184</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395777</t>
+          <t>404184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395777</t>
+          <t>404184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>708977</t>
+          <t>766696</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708977</t>
+          <t>766696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708977</t>
+          <t>766696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183990</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>158647</t>
+          <t>179941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209993</t>
+          <t>237312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>198414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100693</t>
+          <t>174821</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214697</t>
+          <t>223430</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>362343</t>
+          <t>406398</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>273884</t>
+          <t>371822</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>408587</t>
+          <t>444337</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>186265</t>
+          <t>205152</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>176974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212986</t>
+          <t>237013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>243447</t>
+          <t>199843</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191893</t>
+          <t>176961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>354935</t>
+          <t>223464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>429711</t>
+          <t>404995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376846</t>
+          <t>369558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>541322</t>
+          <t>442243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>47979</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77992</t>
+          <t>91055</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49338</t>
+          <t>74630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100339</t>
+          <t>112746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>116366</t>
+          <t>139034</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87406</t>
+          <t>115227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143423</t>
+          <t>165248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,27 +1668,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>21411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>250711</t>
+          <t>288698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227677</t>
+          <t>262899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276280</t>
+          <t>315621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>194126</t>
+          <t>220833</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174644</t>
+          <t>200217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213336</t>
+          <t>241576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>444838</t>
+          <t>509531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412782</t>
+          <t>478929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475573</t>
+          <t>546791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>198722</t>
+          <t>238033</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177194</t>
+          <t>213918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222156</t>
+          <t>266316</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>226732</t>
+          <t>259885</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>206630</t>
+          <t>240299</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>247121</t>
+          <t>280961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>425454</t>
+          <t>497919</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>394938</t>
+          <t>466031</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>454661</t>
+          <t>531907</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68897</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86552</t>
+          <t>95774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97583</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81352</t>
+          <t>98834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110960</t>
+          <t>134027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>166481</t>
+          <t>189009</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>167893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190865</t>
+          <t>214380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>44600</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>33394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541681</t>
+          <t>621300</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541681</t>
+          <t>621300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541681</t>
+          <t>621300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1076738</t>
+          <t>1241058</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1076738</t>
+          <t>1241058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1076738</t>
+          <t>1241058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>494552</t>
+          <t>271543</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>244712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>714982</t>
+          <t>298362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>193292</t>
+          <t>211884</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162566</t>
+          <t>191581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>214288</t>
+          <t>231725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>687844</t>
+          <t>483427</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>509211</t>
+          <t>450052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1055683</t>
+          <t>523827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>283801</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126626</t>
+          <t>282571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>405192</t>
+          <t>336615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>343967</t>
+          <t>339896</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316919</t>
+          <t>320105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400010</t>
+          <t>362112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>627768</t>
+          <t>648483</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377167</t>
+          <t>609161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>760832</t>
+          <t>686083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>95852</t>
+          <t>106191</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>87066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142611</t>
+          <t>127414</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148597</t>
+          <t>155082</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>137327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>171472</t>
+          <t>171217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>244450</t>
+          <t>261273</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150506</t>
+          <t>235688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>304296</t>
+          <t>289094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>37236</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>710516</t>
+          <t>734476</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710516</t>
+          <t>734476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>710516</t>
+          <t>734476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1597298</t>
+          <t>1434159</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1597298</t>
+          <t>1434159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1597298</t>
+          <t>1434159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>199152</t>
+          <t>217459</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>178164</t>
+          <t>194838</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221171</t>
+          <t>239634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>147138</t>
+          <t>163765</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130276</t>
+          <t>147006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161949</t>
+          <t>178989</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>346290</t>
+          <t>381224</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>320498</t>
+          <t>353479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>373304</t>
+          <t>408929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>255090</t>
+          <t>278588</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>232938</t>
+          <t>256110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>276274</t>
+          <t>301399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>241967</t>
+          <t>268675</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224106</t>
+          <t>251275</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258405</t>
+          <t>286919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>497056</t>
+          <t>547263</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>471109</t>
+          <t>518441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>527450</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>90803</t>
+          <t>96244</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107325</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>131854</t>
+          <t>145713</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118506</t>
+          <t>130817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147131</t>
+          <t>163241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>222657</t>
+          <t>241956</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199783</t>
+          <t>217476</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>243178</t>
+          <t>266416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>57955</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545956</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545956</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545956</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1106647</t>
+          <t>1215493</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1106647</t>
+          <t>1215493</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1106647</t>
+          <t>1215493</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,102 +3570,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>132673</t>
+          <t>146528</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117976</t>
+          <t>130869</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149332</t>
+          <t>163820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>124878</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>111155</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>138227</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>31,47%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>271407</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>250185</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>292895</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>32,11%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>116210</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>50456</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>181836</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>248883</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>128240</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>324476</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>171830</t>
+          <t>190765</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>156196</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>186424</t>
+          <t>207762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>392160</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>275508</t>
+          <t>188295</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>511952</t>
+          <t>219307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>563990</t>
+          <t>394928</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>445288</t>
+          <t>370909</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>757698</t>
+          <t>418623</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>56685</t>
+          <t>62142</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40217</t>
+          <t>83024</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>137909</t>
+          <t>108964</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>143877</t>
+          <t>157137</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>142454</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>188239</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>367356</t>
+          <t>406192</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>975724</t>
+          <t>845358</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>975724</t>
+          <t>845358</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>975724</t>
+          <t>845358</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>88232</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76622</t>
+          <t>82609</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101657</t>
+          <t>110367</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>78702</t>
+          <t>86806</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>68209</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>91450</t>
+          <t>101978</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>166934</t>
+          <t>183620</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>150788</t>
+          <t>165420</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>185035</t>
+          <t>201385</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>131366</t>
+          <t>143405</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>117156</t>
+          <t>128865</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>158092</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>203196</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>188119</t>
+          <t>205222</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>217265</t>
+          <t>237158</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>334561</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>315820</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>353855</t>
+          <t>384791</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>60502</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>44941</t>
+          <t>49992</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>72782</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>125442</t>
+          <t>136501</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>113492</t>
+          <t>121858</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139662</t>
+          <t>151818</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>179763</t>
+          <t>197003</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>163182</t>
+          <t>179628</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>196199</t>
+          <t>216705</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>280224</t>
+          <t>307486</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>280224</t>
+          <t>307486</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>280224</t>
+          <t>307486</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>419645</t>
+          <t>457965</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>419645</t>
+          <t>457965</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>419645</t>
+          <t>457965</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>699869</t>
+          <t>765451</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>699869</t>
+          <t>765451</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>699869</t>
+          <t>765451</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1600317</t>
+          <t>1485169</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1438132</t>
+          <t>1422560</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2033608</t>
+          <t>1554014</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1077472</t>
+          <t>1199519</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>870466</t>
+          <t>1147101</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1178093</t>
+          <t>1251858</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2677789</t>
+          <t>2684688</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2426709</t>
+          <t>2595396</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3146648</t>
+          <t>2768743</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1344552</t>
+          <t>1484787</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1025184</t>
+          <t>1425522</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1466512</t>
+          <t>1553364</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1754527</t>
+          <t>1616578</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1598905</t>
+          <t>1563148</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2131137</t>
+          <t>1668082</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>3099079</t>
+          <t>3101365</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2799199</t>
+          <t>3016646</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3491270</t>
+          <t>3191830</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>432223</t>
+          <t>475437</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>330959</t>
+          <t>433688</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>488097</t>
+          <t>518150</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>704641</t>
+          <t>779756</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>569020</t>
+          <t>740827</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>770538</t>
+          <t>823591</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1136864</t>
+          <t>1255193</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>984445</t>
+          <t>1195819</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1235354</t>
+          <t>1318389</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>53257</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>92291</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>94329</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133989</t>
+          <t>150211</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>186572</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>153923</t>
+          <t>178611</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>214137</t>
+          <t>235062</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
